--- a/public/data/Student_List_All_Classes.xlsx
+++ b/public/data/Student_List_All_Classes.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI27"/>
+  <dimension ref="A1:AI28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1717,6 +1717,36 @@
       <c r="AI27" t="inlineStr">
         <is>
           <t>class_1/class-1-ramdev-suthar.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>HEMA RATAWA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>DINESH KUMAR RATAWA</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ARCHANA DEVI</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>14/12/2019</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>class_1/class-1-hema.jpg</t>
         </is>
       </c>
     </row>
